--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAE2DE4-CD55-48DE-B199-03BFA6E92BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF325CC4-E2FE-48FF-AFD8-BCCF67C6C63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,7 +376,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -425,12 +425,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -438,43 +432,46 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1532,80 +1529,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="38" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="24"/>
+      <c r="V1" s="24"/>
+      <c r="W1" s="24"/>
+      <c r="X1" s="24"/>
+      <c r="Y1" s="24"/>
+      <c r="Z1" s="24"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
     </row>
     <row r="2" spans="1:33" s="13" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="38" t="s">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
     </row>
     <row r="3" spans="1:33" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="16"/>
@@ -1643,49 +1640,49 @@
       <c r="AG3" s="14"/>
     </row>
     <row r="4" spans="1:33" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
-      <c r="AG4" s="35"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="36"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="36"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="36"/>
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="36"/>
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="37"/>
     </row>
     <row r="5" spans="1:33" s="10" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="28"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="11">
         <v>1</v>
       </c>
@@ -1787,37 +1784,37 @@
       <c r="B6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
     </row>
     <row r="7" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="9">
@@ -1826,37 +1823,37 @@
       <c r="B7" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="22"/>
-      <c r="AG7" s="22"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
     </row>
     <row r="8" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="9">
@@ -1865,37 +1862,37 @@
       <c r="B8" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="22"/>
-      <c r="AE8" s="22"/>
-      <c r="AF8" s="22"/>
-      <c r="AG8" s="22"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
     </row>
     <row r="9" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="9">
@@ -1904,37 +1901,37 @@
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
     </row>
     <row r="10" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A10" s="9">
@@ -1943,37 +1940,37 @@
       <c r="B10" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="22"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
     </row>
     <row r="11" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="9">
@@ -1982,37 +1979,37 @@
       <c r="B11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
     </row>
     <row r="12" spans="1:33" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="9">
@@ -2021,37 +2018,37 @@
       <c r="B12" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="22"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
     </row>
     <row r="13" spans="1:33" ht="15.75" customHeight="1">
       <c r="A13" s="9">
@@ -2060,37 +2057,37 @@
       <c r="B13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
-      <c r="AE13" s="23"/>
-      <c r="AF13" s="23"/>
-      <c r="AG13" s="23"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="21"/>
+      <c r="V13" s="21"/>
+      <c r="W13" s="21"/>
+      <c r="X13" s="21"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
+      <c r="AF13" s="21"/>
+      <c r="AG13" s="21"/>
     </row>
     <row r="14" spans="1:33" ht="15.75" customHeight="1">
       <c r="A14" s="9">
@@ -2099,37 +2096,37 @@
       <c r="B14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="23"/>
-      <c r="Q14" s="23"/>
-      <c r="R14" s="23"/>
-      <c r="S14" s="23"/>
-      <c r="T14" s="23"/>
-      <c r="U14" s="23"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
     </row>
     <row r="15" spans="1:33" ht="15.75" customHeight="1">
       <c r="A15" s="9">
@@ -2138,37 +2135,37 @@
       <c r="B15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="23"/>
-      <c r="AC15" s="23"/>
-      <c r="AD15" s="23"/>
-      <c r="AE15" s="23"/>
-      <c r="AF15" s="23"/>
-      <c r="AG15" s="23"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="21"/>
+      <c r="AC15" s="21"/>
+      <c r="AD15" s="21"/>
+      <c r="AE15" s="21"/>
+      <c r="AF15" s="21"/>
+      <c r="AG15" s="21"/>
     </row>
     <row r="16" spans="1:33" ht="15.75" customHeight="1">
       <c r="A16" s="9">
@@ -2177,174 +2174,174 @@
       <c r="B16" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="23"/>
-      <c r="Q16" s="23"/>
-      <c r="R16" s="23"/>
-      <c r="S16" s="23"/>
-      <c r="T16" s="23"/>
-      <c r="U16" s="23"/>
-      <c r="V16" s="23"/>
-      <c r="W16" s="23"/>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="23"/>
-      <c r="AC16" s="23"/>
-      <c r="AD16" s="23"/>
-      <c r="AE16" s="23"/>
-      <c r="AF16" s="23"/>
-      <c r="AG16" s="23"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+      <c r="T16" s="21"/>
+      <c r="U16" s="21"/>
+      <c r="V16" s="21"/>
+      <c r="W16" s="21"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="21"/>
+      <c r="AC16" s="21"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="21"/>
+      <c r="AF16" s="21"/>
+      <c r="AG16" s="21"/>
     </row>
     <row r="17" spans="1:33" ht="22.5" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="27"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="27"/>
-      <c r="Y17" s="37"/>
-      <c r="Z17" s="27"/>
-      <c r="AA17" s="37"/>
-      <c r="AB17" s="27"/>
-      <c r="AC17" s="27"/>
-      <c r="AD17" s="27"/>
-      <c r="AE17" s="27"/>
-      <c r="AF17" s="27"/>
-      <c r="AG17" s="27"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1">
       <c r="B18" s="6"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="28"/>
-      <c r="W18" s="28"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="28"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="28"/>
-      <c r="AG18" s="28"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="26"/>
+      <c r="V18" s="26"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="26"/>
+      <c r="Y18" s="26"/>
+      <c r="Z18" s="26"/>
+      <c r="AA18" s="26"/>
+      <c r="AB18" s="26"/>
+      <c r="AC18" s="26"/>
+      <c r="AD18" s="26"/>
+      <c r="AE18" s="26"/>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="26"/>
     </row>
     <row r="19" spans="1:33" ht="22.5" customHeight="1">
       <c r="B19" s="6"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="29"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="29"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="29"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="29"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="29"/>
-      <c r="AG19" s="29"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
     </row>
     <row r="20" spans="1:33" ht="22.5" customHeight="1">
       <c r="B20" s="6"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="28"/>
-      <c r="AF20" s="28"/>
-      <c r="AG20" s="28"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
+      <c r="S20" s="26"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="26"/>
+      <c r="V20" s="26"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="26"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="26"/>
+      <c r="AA20" s="26"/>
+      <c r="AB20" s="26"/>
+      <c r="AC20" s="26"/>
+      <c r="AD20" s="26"/>
+      <c r="AE20" s="26"/>
+      <c r="AF20" s="26"/>
+      <c r="AG20" s="26"/>
     </row>
     <row r="21" spans="1:33" ht="19.5" customHeight="1">
       <c r="B21" s="17" t="s">
@@ -2352,57 +2349,57 @@
       </c>
     </row>
     <row r="22" spans="1:33" ht="242.25" customHeight="1">
-      <c r="B22" s="21"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
-      <c r="AE22" s="20"/>
-      <c r="AF22" s="20"/>
-      <c r="AG22" s="20"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39"/>
+      <c r="S22" s="39"/>
+      <c r="T22" s="39"/>
+      <c r="U22" s="39"/>
+      <c r="V22" s="39"/>
+      <c r="W22" s="39"/>
+      <c r="X22" s="39"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="39"/>
+      <c r="AA22" s="39"/>
+      <c r="AB22" s="39"/>
+      <c r="AC22" s="39"/>
+      <c r="AD22" s="39"/>
+      <c r="AE22" s="39"/>
+      <c r="AF22" s="39"/>
+      <c r="AG22" s="39"/>
     </row>
     <row r="23" spans="1:33" ht="23.25" customHeight="1"/>
     <row r="24" spans="1:33" ht="21" customHeight="1">
       <c r="AA24" s="5"/>
       <c r="AB24" s="5"/>
-      <c r="AC24" s="25"/>
-      <c r="AD24" s="26"/>
-      <c r="AE24" s="26"/>
-      <c r="AF24" s="26"/>
-      <c r="AG24" s="26"/>
+      <c r="AC24" s="38"/>
+      <c r="AD24" s="31"/>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
     </row>
     <row r="25" spans="1:33" ht="29.25" customHeight="1">
-      <c r="AC25" s="36" t="s">
+      <c r="AC25" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AD25" s="26"/>
-      <c r="AE25" s="26"/>
-      <c r="AF25" s="26"/>
-      <c r="AG25" s="26"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
     </row>
     <row r="26" spans="1:33" ht="7.5" customHeight="1">
       <c r="D26" s="4"/>
@@ -2414,7 +2411,62 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="B22:AG22"/>
+    <mergeCell ref="AC24:AG24"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="AE17:AE18"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="Y19:Y20"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="S19:S20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="AA19:AA20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="X19:X20"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="AG17:AG18"/>
+    <mergeCell ref="AD19:AD20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="T19:T20"/>
+    <mergeCell ref="AC25:AG25"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="AE19:AE20"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="Z19:Z20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="AC17:AC18"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="AD17:AD18"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="AB19:AB20"/>
     <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="N19:N20"/>
     <mergeCell ref="P19:P20"/>
@@ -2431,60 +2483,6 @@
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="O17:O18"/>
-    <mergeCell ref="AC25:AG25"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="AE19:AE20"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="Z19:Z20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="AC17:AC18"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="AD17:AD18"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="AB19:AB20"/>
-    <mergeCell ref="AD19:AD20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="L19:L20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="T19:T20"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="S19:S20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="AA19:AA20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="X19:X20"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="AG17:AG18"/>
-    <mergeCell ref="AC24:AG24"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="AE17:AE18"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="Y19:Y20"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="X17:X18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -1769,8 +1769,16 @@
       <c r="AB6" s="20" t="n"/>
       <c r="AC6" s="20" t="n"/>
       <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="20" t="n"/>
-      <c r="AF6" s="20" t="n"/>
+      <c r="AE6" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="20" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1810,8 +1818,16 @@
       <c r="AB7" s="20" t="n"/>
       <c r="AC7" s="20" t="n"/>
       <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="20" t="n"/>
-      <c r="AF7" s="20" t="n"/>
+      <c r="AE7" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="20" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1851,8 +1867,16 @@
       <c r="AB8" s="20" t="n"/>
       <c r="AC8" s="20" t="n"/>
       <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="20" t="n"/>
-      <c r="AF8" s="20" t="n"/>
+      <c r="AE8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="20" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1892,8 +1916,16 @@
       <c r="AB9" s="20" t="n"/>
       <c r="AC9" s="20" t="n"/>
       <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="20" t="n"/>
-      <c r="AF9" s="20" t="n"/>
+      <c r="AE9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="20" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1933,8 +1965,16 @@
       <c r="AB10" s="20" t="n"/>
       <c r="AC10" s="20" t="n"/>
       <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="20" t="n"/>
-      <c r="AF10" s="20" t="n"/>
+      <c r="AE10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="20" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -1974,8 +2014,16 @@
       <c r="AB11" s="20" t="n"/>
       <c r="AC11" s="20" t="n"/>
       <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="20" t="n"/>
-      <c r="AF11" s="20" t="n"/>
+      <c r="AE11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG11" s="20" t="n"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="10">
@@ -2015,8 +2063,16 @@
       <c r="AB12" s="20" t="n"/>
       <c r="AC12" s="20" t="n"/>
       <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="20" t="n"/>
-      <c r="AF12" s="20" t="n"/>
+      <c r="AE12" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF12" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AG12" s="20" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -2056,8 +2112,16 @@
       <c r="AB13" s="21" t="n"/>
       <c r="AC13" s="21" t="n"/>
       <c r="AD13" s="21" t="n"/>
-      <c r="AE13" s="21" t="n"/>
-      <c r="AF13" s="21" t="n"/>
+      <c r="AE13" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF13" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG13" s="21" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -2097,8 +2161,16 @@
       <c r="AB14" s="21" t="n"/>
       <c r="AC14" s="21" t="n"/>
       <c r="AD14" s="21" t="n"/>
-      <c r="AE14" s="21" t="n"/>
-      <c r="AF14" s="21" t="n"/>
+      <c r="AE14" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF14" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG14" s="21" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -2138,8 +2210,16 @@
       <c r="AB15" s="21" t="n"/>
       <c r="AC15" s="21" t="n"/>
       <c r="AD15" s="21" t="n"/>
-      <c r="AE15" s="21" t="n"/>
-      <c r="AF15" s="21" t="n"/>
+      <c r="AE15" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF15" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG15" s="21" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -2179,8 +2259,16 @@
       <c r="AB16" s="21" t="n"/>
       <c r="AC16" s="21" t="n"/>
       <c r="AD16" s="21" t="n"/>
-      <c r="AE16" s="21" t="n"/>
-      <c r="AF16" s="21" t="n"/>
+      <c r="AE16" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF16" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG16" s="21" t="n"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
@@ -2214,8 +2302,16 @@
       <c r="AB17" s="28" t="n"/>
       <c r="AC17" s="28" t="n"/>
       <c r="AD17" s="28" t="n"/>
-      <c r="AE17" s="28" t="n"/>
-      <c r="AF17" s="28" t="n"/>
+      <c r="AE17" s="32" t="inlineStr">
+        <is>
+          <t>ชาญวิทย์</t>
+        </is>
+      </c>
+      <c r="AF17" s="32" t="inlineStr">
+        <is>
+          <t>ชาญวิทย์</t>
+        </is>
+      </c>
       <c r="AG17" s="28" t="n"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
@@ -2328,7 +2424,7 @@
       </c>
     </row>
     <row r="22" ht="242.25" customHeight="1">
-      <c r="B22" s="39" t="n"/>
+      <c r="B22" s="39" t="inlineStr"/>
     </row>
     <row r="23" ht="23.25" customHeight="1"/>
     <row r="24" ht="21" customHeight="1">

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -430,6 +430,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1741,45 +1744,37 @@
           <t>Worm Spindle ก่อนเริมงาน ตรวจสอบความ ผิดปกติของชุด  Back gauge  และ Motor</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="20" t="n"/>
-      <c r="O6" s="20" t="n"/>
-      <c r="P6" s="20" t="n"/>
-      <c r="Q6" s="20" t="n"/>
-      <c r="R6" s="20" t="n"/>
-      <c r="S6" s="20" t="n"/>
-      <c r="T6" s="20" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="W6" s="20" t="n"/>
-      <c r="X6" s="20" t="n"/>
-      <c r="Y6" s="20" t="n"/>
-      <c r="Z6" s="20" t="n"/>
-      <c r="AA6" s="20" t="n"/>
-      <c r="AB6" s="20" t="n"/>
-      <c r="AC6" s="20" t="n"/>
-      <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="20" t="n"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+      <c r="K6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="20" t="inlineStr"/>
+      <c r="R6" s="20" t="inlineStr"/>
+      <c r="S6" s="20" t="inlineStr"/>
+      <c r="T6" s="20" t="inlineStr"/>
+      <c r="U6" s="20" t="inlineStr"/>
+      <c r="V6" s="20" t="inlineStr"/>
+      <c r="W6" s="20" t="inlineStr"/>
+      <c r="X6" s="20" t="inlineStr"/>
+      <c r="Y6" s="20" t="inlineStr"/>
+      <c r="Z6" s="20" t="inlineStr"/>
+      <c r="AA6" s="20" t="inlineStr"/>
+      <c r="AB6" s="20" t="inlineStr"/>
+      <c r="AC6" s="20" t="inlineStr"/>
+      <c r="AD6" s="20" t="inlineStr"/>
+      <c r="AE6" s="20" t="inlineStr"/>
+      <c r="AF6" s="20" t="inlineStr"/>
+      <c r="AG6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A7" s="9" t="n">
@@ -1790,45 +1785,37 @@
           <t>เช็ค Auto  Up-Down back gauge  และ Manual ( ความคร่องตัวในการเคลื่อนที่ของ Spindle )</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="20" t="n"/>
-      <c r="P7" s="20" t="n"/>
-      <c r="Q7" s="20" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="S7" s="20" t="n"/>
-      <c r="T7" s="20" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="20" t="n"/>
-      <c r="W7" s="20" t="n"/>
-      <c r="X7" s="20" t="n"/>
-      <c r="Y7" s="20" t="n"/>
-      <c r="Z7" s="20" t="n"/>
-      <c r="AA7" s="20" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="20" t="n"/>
-      <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="20" t="n"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr"/>
+      <c r="K7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr"/>
+      <c r="M7" s="20" t="inlineStr"/>
+      <c r="N7" s="20" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr"/>
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="20" t="inlineStr"/>
+      <c r="R7" s="20" t="inlineStr"/>
+      <c r="S7" s="20" t="inlineStr"/>
+      <c r="T7" s="20" t="inlineStr"/>
+      <c r="U7" s="20" t="inlineStr"/>
+      <c r="V7" s="20" t="inlineStr"/>
+      <c r="W7" s="20" t="inlineStr"/>
+      <c r="X7" s="20" t="inlineStr"/>
+      <c r="Y7" s="20" t="inlineStr"/>
+      <c r="Z7" s="20" t="inlineStr"/>
+      <c r="AA7" s="20" t="inlineStr"/>
+      <c r="AB7" s="20" t="inlineStr"/>
+      <c r="AC7" s="20" t="inlineStr"/>
+      <c r="AD7" s="20" t="inlineStr"/>
+      <c r="AE7" s="20" t="inlineStr"/>
+      <c r="AF7" s="20" t="inlineStr"/>
+      <c r="AG7" s="20" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A8" s="9" t="n">
@@ -1839,45 +1826,37 @@
           <t>ตรวจสอบการ SLIDE  ของแกน X</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="n"/>
-      <c r="P8" s="20" t="n"/>
-      <c r="Q8" s="20" t="n"/>
-      <c r="R8" s="20" t="n"/>
-      <c r="S8" s="20" t="n"/>
-      <c r="T8" s="20" t="n"/>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="20" t="n"/>
-      <c r="W8" s="20" t="n"/>
-      <c r="X8" s="20" t="n"/>
-      <c r="Y8" s="20" t="n"/>
-      <c r="Z8" s="20" t="n"/>
-      <c r="AA8" s="20" t="n"/>
-      <c r="AB8" s="20" t="n"/>
-      <c r="AC8" s="20" t="n"/>
-      <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="20" t="n"/>
+      <c r="C8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
+      <c r="F8" s="20" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr"/>
+      <c r="K8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr"/>
+      <c r="N8" s="20" t="inlineStr"/>
+      <c r="O8" s="20" t="inlineStr"/>
+      <c r="P8" s="20" t="inlineStr"/>
+      <c r="Q8" s="20" t="inlineStr"/>
+      <c r="R8" s="20" t="inlineStr"/>
+      <c r="S8" s="20" t="inlineStr"/>
+      <c r="T8" s="20" t="inlineStr"/>
+      <c r="U8" s="20" t="inlineStr"/>
+      <c r="V8" s="20" t="inlineStr"/>
+      <c r="W8" s="20" t="inlineStr"/>
+      <c r="X8" s="20" t="inlineStr"/>
+      <c r="Y8" s="20" t="inlineStr"/>
+      <c r="Z8" s="20" t="inlineStr"/>
+      <c r="AA8" s="20" t="inlineStr"/>
+      <c r="AB8" s="20" t="inlineStr"/>
+      <c r="AC8" s="20" t="inlineStr"/>
+      <c r="AD8" s="20" t="inlineStr"/>
+      <c r="AE8" s="20" t="inlineStr"/>
+      <c r="AF8" s="20" t="inlineStr"/>
+      <c r="AG8" s="20" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A9" s="9" t="n">
@@ -1888,45 +1867,37 @@
           <t>ตรวจสอบการ SLIDE  ของแกน Y</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="20" t="n"/>
-      <c r="P9" s="20" t="n"/>
-      <c r="Q9" s="20" t="n"/>
-      <c r="R9" s="20" t="n"/>
-      <c r="S9" s="20" t="n"/>
-      <c r="T9" s="20" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="20" t="n"/>
-      <c r="W9" s="20" t="n"/>
-      <c r="X9" s="20" t="n"/>
-      <c r="Y9" s="20" t="n"/>
-      <c r="Z9" s="20" t="n"/>
-      <c r="AA9" s="20" t="n"/>
-      <c r="AB9" s="20" t="n"/>
-      <c r="AC9" s="20" t="n"/>
-      <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="20" t="n"/>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+      <c r="K9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr"/>
+      <c r="M9" s="20" t="inlineStr"/>
+      <c r="N9" s="20" t="inlineStr"/>
+      <c r="O9" s="20" t="inlineStr"/>
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="20" t="inlineStr"/>
+      <c r="R9" s="20" t="inlineStr"/>
+      <c r="S9" s="20" t="inlineStr"/>
+      <c r="T9" s="20" t="inlineStr"/>
+      <c r="U9" s="20" t="inlineStr"/>
+      <c r="V9" s="20" t="inlineStr"/>
+      <c r="W9" s="20" t="inlineStr"/>
+      <c r="X9" s="20" t="inlineStr"/>
+      <c r="Y9" s="20" t="inlineStr"/>
+      <c r="Z9" s="20" t="inlineStr"/>
+      <c r="AA9" s="20" t="inlineStr"/>
+      <c r="AB9" s="20" t="inlineStr"/>
+      <c r="AC9" s="20" t="inlineStr"/>
+      <c r="AD9" s="20" t="inlineStr"/>
+      <c r="AE9" s="20" t="inlineStr"/>
+      <c r="AF9" s="20" t="inlineStr"/>
+      <c r="AG9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A10" s="9" t="n">
@@ -1937,45 +1908,37 @@
           <t>ตรวจสอบการ SLIDE  ของแกน Z</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="20" t="n"/>
-      <c r="P10" s="20" t="n"/>
-      <c r="Q10" s="20" t="n"/>
-      <c r="R10" s="20" t="n"/>
-      <c r="S10" s="20" t="n"/>
-      <c r="T10" s="20" t="n"/>
-      <c r="U10" s="20" t="n"/>
-      <c r="V10" s="20" t="n"/>
-      <c r="W10" s="20" t="n"/>
-      <c r="X10" s="20" t="n"/>
-      <c r="Y10" s="20" t="n"/>
-      <c r="Z10" s="20" t="n"/>
-      <c r="AA10" s="20" t="n"/>
-      <c r="AB10" s="20" t="n"/>
-      <c r="AC10" s="20" t="n"/>
-      <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="20" t="n"/>
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr"/>
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr"/>
+      <c r="N10" s="20" t="inlineStr"/>
+      <c r="O10" s="20" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr"/>
+      <c r="Q10" s="20" t="inlineStr"/>
+      <c r="R10" s="20" t="inlineStr"/>
+      <c r="S10" s="20" t="inlineStr"/>
+      <c r="T10" s="20" t="inlineStr"/>
+      <c r="U10" s="20" t="inlineStr"/>
+      <c r="V10" s="20" t="inlineStr"/>
+      <c r="W10" s="20" t="inlineStr"/>
+      <c r="X10" s="20" t="inlineStr"/>
+      <c r="Y10" s="20" t="inlineStr"/>
+      <c r="Z10" s="20" t="inlineStr"/>
+      <c r="AA10" s="20" t="inlineStr"/>
+      <c r="AB10" s="20" t="inlineStr"/>
+      <c r="AC10" s="20" t="inlineStr"/>
+      <c r="AD10" s="20" t="inlineStr"/>
+      <c r="AE10" s="20" t="inlineStr"/>
+      <c r="AF10" s="20" t="inlineStr"/>
+      <c r="AG10" s="20" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A11" s="9" t="n">
@@ -1986,45 +1949,37 @@
           <t>ระดับน้ำมันไฮดรอลิค ตรวจสอบน้ำมันในปั้มน้ำมันหล่อ ลื่นแกน  X,Y,Z</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="20" t="n"/>
-      <c r="P11" s="20" t="n"/>
-      <c r="Q11" s="20" t="n"/>
-      <c r="R11" s="20" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="U11" s="20" t="n"/>
-      <c r="V11" s="20" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="20" t="n"/>
-      <c r="Y11" s="20" t="n"/>
-      <c r="Z11" s="20" t="n"/>
-      <c r="AA11" s="20" t="n"/>
-      <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="20" t="n"/>
-      <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="20" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG11" s="20" t="n"/>
+      <c r="C11" s="20" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr"/>
+      <c r="E11" s="20" t="inlineStr"/>
+      <c r="F11" s="20" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
+      <c r="M11" s="20" t="inlineStr"/>
+      <c r="N11" s="20" t="inlineStr"/>
+      <c r="O11" s="20" t="inlineStr"/>
+      <c r="P11" s="20" t="inlineStr"/>
+      <c r="Q11" s="20" t="inlineStr"/>
+      <c r="R11" s="20" t="inlineStr"/>
+      <c r="S11" s="20" t="inlineStr"/>
+      <c r="T11" s="20" t="inlineStr"/>
+      <c r="U11" s="20" t="inlineStr"/>
+      <c r="V11" s="20" t="inlineStr"/>
+      <c r="W11" s="20" t="inlineStr"/>
+      <c r="X11" s="20" t="inlineStr"/>
+      <c r="Y11" s="20" t="inlineStr"/>
+      <c r="Z11" s="20" t="inlineStr"/>
+      <c r="AA11" s="20" t="inlineStr"/>
+      <c r="AB11" s="20" t="inlineStr"/>
+      <c r="AC11" s="20" t="inlineStr"/>
+      <c r="AD11" s="20" t="inlineStr"/>
+      <c r="AE11" s="20" t="inlineStr"/>
+      <c r="AF11" s="20" t="inlineStr"/>
+      <c r="AG11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="10">
       <c r="A12" s="9" t="n">
@@ -2035,45 +1990,37 @@
           <t>ตรวจน้ำมันหล่อลื่นเย็น ตรวจสอบการทำงานของปั้ม COOLANT และสภาพของน้ำ  COOLANT</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="20" t="n"/>
-      <c r="P12" s="20" t="n"/>
-      <c r="Q12" s="20" t="n"/>
-      <c r="R12" s="20" t="n"/>
-      <c r="S12" s="20" t="n"/>
-      <c r="T12" s="20" t="n"/>
-      <c r="U12" s="20" t="n"/>
-      <c r="V12" s="20" t="n"/>
-      <c r="W12" s="20" t="n"/>
-      <c r="X12" s="20" t="n"/>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="20" t="n"/>
-      <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="20" t="n"/>
-      <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF12" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG12" s="20" t="n"/>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr"/>
+      <c r="Q12" s="20" t="inlineStr"/>
+      <c r="R12" s="20" t="inlineStr"/>
+      <c r="S12" s="20" t="inlineStr"/>
+      <c r="T12" s="20" t="inlineStr"/>
+      <c r="U12" s="20" t="inlineStr"/>
+      <c r="V12" s="20" t="inlineStr"/>
+      <c r="W12" s="20" t="inlineStr"/>
+      <c r="X12" s="20" t="inlineStr"/>
+      <c r="Y12" s="20" t="inlineStr"/>
+      <c r="Z12" s="20" t="inlineStr"/>
+      <c r="AA12" s="20" t="inlineStr"/>
+      <c r="AB12" s="20" t="inlineStr"/>
+      <c r="AC12" s="20" t="inlineStr"/>
+      <c r="AD12" s="20" t="inlineStr"/>
+      <c r="AE12" s="20" t="inlineStr"/>
+      <c r="AF12" s="20" t="inlineStr"/>
+      <c r="AG12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="9" t="n">
@@ -2084,45 +2031,37 @@
           <t>ตรวจสอบหน้าจอ  DIGITAL READ OUT และการทำ งานของ LINEAR SCALE</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
-      <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="21" t="n"/>
-      <c r="T13" s="21" t="n"/>
-      <c r="U13" s="21" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="21" t="n"/>
-      <c r="X13" s="21" t="n"/>
-      <c r="Y13" s="22" t="n"/>
-      <c r="Z13" s="21" t="n"/>
-      <c r="AA13" s="22" t="n"/>
-      <c r="AB13" s="21" t="n"/>
-      <c r="AC13" s="21" t="n"/>
-      <c r="AD13" s="21" t="n"/>
-      <c r="AE13" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF13" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG13" s="21" t="n"/>
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="21" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
+      <c r="K13" s="21" t="inlineStr"/>
+      <c r="L13" s="21" t="inlineStr"/>
+      <c r="M13" s="21" t="inlineStr"/>
+      <c r="N13" s="21" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr"/>
+      <c r="P13" s="21" t="inlineStr"/>
+      <c r="Q13" s="21" t="inlineStr"/>
+      <c r="R13" s="21" t="inlineStr"/>
+      <c r="S13" s="21" t="inlineStr"/>
+      <c r="T13" s="21" t="inlineStr"/>
+      <c r="U13" s="21" t="inlineStr"/>
+      <c r="V13" s="21" t="inlineStr"/>
+      <c r="W13" s="21" t="inlineStr"/>
+      <c r="X13" s="21" t="inlineStr"/>
+      <c r="Y13" s="22" t="inlineStr"/>
+      <c r="Z13" s="21" t="inlineStr"/>
+      <c r="AA13" s="22" t="inlineStr"/>
+      <c r="AB13" s="21" t="inlineStr"/>
+      <c r="AC13" s="21" t="inlineStr"/>
+      <c r="AD13" s="21" t="inlineStr"/>
+      <c r="AE13" s="22" t="inlineStr"/>
+      <c r="AF13" s="22" t="inlineStr"/>
+      <c r="AG13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="9" t="n">
@@ -2133,45 +2072,37 @@
           <t>หยอดน้ำมันหล่อลื่นทุกวันจันทร์</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
-      <c r="P14" s="21" t="n"/>
-      <c r="Q14" s="21" t="n"/>
-      <c r="R14" s="21" t="n"/>
-      <c r="S14" s="21" t="n"/>
-      <c r="T14" s="21" t="n"/>
-      <c r="U14" s="21" t="n"/>
-      <c r="V14" s="21" t="n"/>
-      <c r="W14" s="21" t="n"/>
-      <c r="X14" s="21" t="n"/>
-      <c r="Y14" s="22" t="n"/>
-      <c r="Z14" s="21" t="n"/>
-      <c r="AA14" s="22" t="n"/>
-      <c r="AB14" s="21" t="n"/>
-      <c r="AC14" s="21" t="n"/>
-      <c r="AD14" s="21" t="n"/>
-      <c r="AE14" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF14" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG14" s="21" t="n"/>
+      <c r="C14" s="21" t="inlineStr"/>
+      <c r="D14" s="21" t="inlineStr"/>
+      <c r="E14" s="21" t="inlineStr"/>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+      <c r="H14" s="21" t="inlineStr"/>
+      <c r="I14" s="21" t="inlineStr"/>
+      <c r="J14" s="21" t="inlineStr"/>
+      <c r="K14" s="21" t="inlineStr"/>
+      <c r="L14" s="21" t="inlineStr"/>
+      <c r="M14" s="21" t="inlineStr"/>
+      <c r="N14" s="21" t="inlineStr"/>
+      <c r="O14" s="21" t="inlineStr"/>
+      <c r="P14" s="21" t="inlineStr"/>
+      <c r="Q14" s="21" t="inlineStr"/>
+      <c r="R14" s="21" t="inlineStr"/>
+      <c r="S14" s="21" t="inlineStr"/>
+      <c r="T14" s="21" t="inlineStr"/>
+      <c r="U14" s="21" t="inlineStr"/>
+      <c r="V14" s="21" t="inlineStr"/>
+      <c r="W14" s="21" t="inlineStr"/>
+      <c r="X14" s="21" t="inlineStr"/>
+      <c r="Y14" s="22" t="inlineStr"/>
+      <c r="Z14" s="21" t="inlineStr"/>
+      <c r="AA14" s="22" t="inlineStr"/>
+      <c r="AB14" s="21" t="inlineStr"/>
+      <c r="AC14" s="21" t="inlineStr"/>
+      <c r="AD14" s="21" t="inlineStr"/>
+      <c r="AE14" s="22" t="inlineStr"/>
+      <c r="AF14" s="22" t="inlineStr"/>
+      <c r="AG14" s="21" t="inlineStr"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="9" t="n">
@@ -2182,45 +2113,37 @@
           <t>ตรวจสอบการทำงานของไฟฟ้าแสงสว่างของเครื่อง</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
-      <c r="P15" s="21" t="n"/>
-      <c r="Q15" s="21" t="n"/>
-      <c r="R15" s="21" t="n"/>
-      <c r="S15" s="21" t="n"/>
-      <c r="T15" s="21" t="n"/>
-      <c r="U15" s="21" t="n"/>
-      <c r="V15" s="21" t="n"/>
-      <c r="W15" s="21" t="n"/>
-      <c r="X15" s="21" t="n"/>
-      <c r="Y15" s="22" t="n"/>
-      <c r="Z15" s="21" t="n"/>
-      <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="21" t="n"/>
-      <c r="AC15" s="21" t="n"/>
-      <c r="AD15" s="21" t="n"/>
-      <c r="AE15" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF15" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG15" s="21" t="n"/>
+      <c r="C15" s="21" t="inlineStr"/>
+      <c r="D15" s="21" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+      <c r="I15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
+      <c r="K15" s="21" t="inlineStr"/>
+      <c r="L15" s="21" t="inlineStr"/>
+      <c r="M15" s="21" t="inlineStr"/>
+      <c r="N15" s="21" t="inlineStr"/>
+      <c r="O15" s="21" t="inlineStr"/>
+      <c r="P15" s="21" t="inlineStr"/>
+      <c r="Q15" s="21" t="inlineStr"/>
+      <c r="R15" s="21" t="inlineStr"/>
+      <c r="S15" s="21" t="inlineStr"/>
+      <c r="T15" s="21" t="inlineStr"/>
+      <c r="U15" s="21" t="inlineStr"/>
+      <c r="V15" s="21" t="inlineStr"/>
+      <c r="W15" s="21" t="inlineStr"/>
+      <c r="X15" s="21" t="inlineStr"/>
+      <c r="Y15" s="22" t="inlineStr"/>
+      <c r="Z15" s="21" t="inlineStr"/>
+      <c r="AA15" s="22" t="inlineStr"/>
+      <c r="AB15" s="21" t="inlineStr"/>
+      <c r="AC15" s="21" t="inlineStr"/>
+      <c r="AD15" s="21" t="inlineStr"/>
+      <c r="AE15" s="22" t="inlineStr"/>
+      <c r="AF15" s="22" t="inlineStr"/>
+      <c r="AG15" s="21" t="inlineStr"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="9" t="n">
@@ -2231,88 +2154,72 @@
           <t>ตรวจสอบสภาพความพร้อมโดยรวมของเครื่องจักร  และอุกรณ์เสริมต่าง ๆ</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
-      <c r="S16" s="21" t="n"/>
-      <c r="T16" s="21" t="n"/>
-      <c r="U16" s="21" t="n"/>
-      <c r="V16" s="21" t="n"/>
-      <c r="W16" s="21" t="n"/>
-      <c r="X16" s="21" t="n"/>
-      <c r="Y16" s="22" t="n"/>
-      <c r="Z16" s="21" t="n"/>
-      <c r="AA16" s="22" t="n"/>
-      <c r="AB16" s="21" t="n"/>
-      <c r="AC16" s="21" t="n"/>
-      <c r="AD16" s="21" t="n"/>
-      <c r="AE16" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF16" s="22" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG16" s="21" t="n"/>
+      <c r="C16" s="21" t="inlineStr"/>
+      <c r="D16" s="21" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr"/>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+      <c r="H16" s="21" t="inlineStr"/>
+      <c r="I16" s="21" t="inlineStr"/>
+      <c r="J16" s="21" t="inlineStr"/>
+      <c r="K16" s="21" t="inlineStr"/>
+      <c r="L16" s="21" t="inlineStr"/>
+      <c r="M16" s="21" t="inlineStr"/>
+      <c r="N16" s="21" t="inlineStr"/>
+      <c r="O16" s="21" t="inlineStr"/>
+      <c r="P16" s="21" t="inlineStr"/>
+      <c r="Q16" s="21" t="inlineStr"/>
+      <c r="R16" s="21" t="inlineStr"/>
+      <c r="S16" s="21" t="inlineStr"/>
+      <c r="T16" s="21" t="inlineStr"/>
+      <c r="U16" s="21" t="inlineStr"/>
+      <c r="V16" s="21" t="inlineStr"/>
+      <c r="W16" s="21" t="inlineStr"/>
+      <c r="X16" s="21" t="inlineStr"/>
+      <c r="Y16" s="22" t="inlineStr"/>
+      <c r="Z16" s="21" t="inlineStr"/>
+      <c r="AA16" s="22" t="inlineStr"/>
+      <c r="AB16" s="21" t="inlineStr"/>
+      <c r="AC16" s="21" t="inlineStr"/>
+      <c r="AD16" s="21" t="inlineStr"/>
+      <c r="AE16" s="22" t="inlineStr"/>
+      <c r="AF16" s="22" t="inlineStr"/>
+      <c r="AG16" s="21" t="inlineStr"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="8" t="n"/>
       <c r="B17" s="7" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="28" t="n"/>
-      <c r="F17" s="28" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="28" t="n"/>
-      <c r="J17" s="28" t="n"/>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="28" t="n"/>
-      <c r="N17" s="28" t="n"/>
-      <c r="O17" s="28" t="n"/>
-      <c r="P17" s="28" t="n"/>
-      <c r="Q17" s="28" t="n"/>
-      <c r="R17" s="28" t="n"/>
-      <c r="S17" s="28" t="n"/>
-      <c r="T17" s="28" t="n"/>
-      <c r="U17" s="28" t="n"/>
-      <c r="V17" s="28" t="n"/>
-      <c r="W17" s="28" t="n"/>
-      <c r="X17" s="28" t="n"/>
-      <c r="Y17" s="32" t="n"/>
-      <c r="Z17" s="28" t="n"/>
-      <c r="AA17" s="32" t="n"/>
-      <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="28" t="n"/>
-      <c r="AD17" s="28" t="n"/>
-      <c r="AE17" s="32" t="inlineStr">
-        <is>
-          <t>ชาญวิทย์</t>
-        </is>
-      </c>
-      <c r="AF17" s="32" t="inlineStr">
-        <is>
-          <t>ชาญวิทย์</t>
-        </is>
-      </c>
-      <c r="AG17" s="28" t="n"/>
+      <c r="C17" s="28" t="inlineStr"/>
+      <c r="D17" s="28" t="inlineStr"/>
+      <c r="E17" s="28" t="inlineStr"/>
+      <c r="F17" s="28" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr"/>
+      <c r="H17" s="28" t="inlineStr"/>
+      <c r="I17" s="28" t="inlineStr"/>
+      <c r="J17" s="28" t="inlineStr"/>
+      <c r="K17" s="28" t="inlineStr"/>
+      <c r="L17" s="28" t="inlineStr"/>
+      <c r="M17" s="28" t="inlineStr"/>
+      <c r="N17" s="28" t="inlineStr"/>
+      <c r="O17" s="28" t="inlineStr"/>
+      <c r="P17" s="28" t="inlineStr"/>
+      <c r="Q17" s="28" t="inlineStr"/>
+      <c r="R17" s="28" t="inlineStr"/>
+      <c r="S17" s="28" t="inlineStr"/>
+      <c r="T17" s="28" t="inlineStr"/>
+      <c r="U17" s="28" t="inlineStr"/>
+      <c r="V17" s="28" t="inlineStr"/>
+      <c r="W17" s="28" t="inlineStr"/>
+      <c r="X17" s="28" t="inlineStr"/>
+      <c r="Y17" s="32" t="inlineStr"/>
+      <c r="Z17" s="28" t="inlineStr"/>
+      <c r="AA17" s="32" t="inlineStr"/>
+      <c r="AB17" s="28" t="inlineStr"/>
+      <c r="AC17" s="28" t="inlineStr"/>
+      <c r="AD17" s="28" t="inlineStr"/>
+      <c r="AE17" s="32" t="inlineStr"/>
+      <c r="AF17" s="32" t="inlineStr"/>
+      <c r="AG17" s="28" t="inlineStr"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="B18" s="6" t="n"/>
@@ -2350,37 +2257,37 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="B19" s="6" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="25" t="n"/>
-      <c r="L19" s="25" t="n"/>
-      <c r="M19" s="25" t="n"/>
-      <c r="N19" s="25" t="n"/>
-      <c r="O19" s="25" t="n"/>
-      <c r="P19" s="25" t="n"/>
-      <c r="Q19" s="25" t="n"/>
-      <c r="R19" s="25" t="n"/>
-      <c r="S19" s="25" t="n"/>
-      <c r="T19" s="25" t="n"/>
-      <c r="U19" s="25" t="n"/>
-      <c r="V19" s="25" t="n"/>
-      <c r="W19" s="25" t="n"/>
-      <c r="X19" s="25" t="n"/>
-      <c r="Y19" s="35" t="n"/>
-      <c r="Z19" s="25" t="n"/>
-      <c r="AA19" s="35" t="n"/>
-      <c r="AB19" s="25" t="n"/>
-      <c r="AC19" s="25" t="n"/>
-      <c r="AD19" s="25" t="n"/>
-      <c r="AE19" s="25" t="n"/>
-      <c r="AF19" s="25" t="n"/>
-      <c r="AG19" s="25" t="n"/>
+      <c r="C19" s="25" t="inlineStr"/>
+      <c r="D19" s="25" t="inlineStr"/>
+      <c r="E19" s="25" t="inlineStr"/>
+      <c r="F19" s="25" t="inlineStr"/>
+      <c r="G19" s="25" t="inlineStr"/>
+      <c r="H19" s="25" t="inlineStr"/>
+      <c r="I19" s="25" t="inlineStr"/>
+      <c r="J19" s="25" t="inlineStr"/>
+      <c r="K19" s="25" t="inlineStr"/>
+      <c r="L19" s="25" t="inlineStr"/>
+      <c r="M19" s="25" t="inlineStr"/>
+      <c r="N19" s="25" t="inlineStr"/>
+      <c r="O19" s="25" t="inlineStr"/>
+      <c r="P19" s="25" t="inlineStr"/>
+      <c r="Q19" s="25" t="inlineStr"/>
+      <c r="R19" s="25" t="inlineStr"/>
+      <c r="S19" s="25" t="inlineStr"/>
+      <c r="T19" s="25" t="inlineStr"/>
+      <c r="U19" s="25" t="inlineStr"/>
+      <c r="V19" s="25" t="inlineStr"/>
+      <c r="W19" s="25" t="inlineStr"/>
+      <c r="X19" s="25" t="inlineStr"/>
+      <c r="Y19" s="35" t="inlineStr"/>
+      <c r="Z19" s="25" t="inlineStr"/>
+      <c r="AA19" s="35" t="inlineStr"/>
+      <c r="AB19" s="25" t="inlineStr"/>
+      <c r="AC19" s="25" t="inlineStr"/>
+      <c r="AD19" s="25" t="inlineStr"/>
+      <c r="AE19" s="25" t="inlineStr"/>
+      <c r="AF19" s="25" t="inlineStr"/>
+      <c r="AG19" s="25" t="inlineStr"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="B20" s="6" t="n"/>
@@ -2424,7 +2331,7 @@
       </c>
     </row>
     <row r="22" ht="242.25" customHeight="1">
-      <c r="B22" s="39" t="inlineStr"/>
+      <c r="B22" s="40" t="inlineStr"/>
     </row>
     <row r="23" ht="23.25" customHeight="1"/>
     <row r="24" ht="21" customHeight="1">

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -1749,7 +1749,11 @@
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="inlineStr"/>
       <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="20" t="inlineStr"/>
       <c r="J6" s="20" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr"/>
@@ -1790,7 +1794,11 @@
       <c r="E7" s="20" t="inlineStr"/>
       <c r="F7" s="20" t="inlineStr"/>
       <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="20" t="inlineStr"/>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
       <c r="K7" s="20" t="inlineStr"/>
@@ -1831,7 +1839,11 @@
       <c r="E8" s="20" t="inlineStr"/>
       <c r="F8" s="20" t="inlineStr"/>
       <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="20" t="inlineStr"/>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
@@ -1872,7 +1884,11 @@
       <c r="E9" s="20" t="inlineStr"/>
       <c r="F9" s="20" t="inlineStr"/>
       <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="20" t="inlineStr"/>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
@@ -1913,7 +1929,11 @@
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="inlineStr"/>
       <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
       <c r="K10" s="20" t="inlineStr"/>
@@ -1954,7 +1974,11 @@
       <c r="E11" s="20" t="inlineStr"/>
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="20" t="inlineStr"/>
-      <c r="H11" s="20" t="inlineStr"/>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="20" t="inlineStr"/>
       <c r="J11" s="20" t="inlineStr"/>
       <c r="K11" s="20" t="inlineStr"/>
@@ -1995,7 +2019,11 @@
       <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="inlineStr"/>
       <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="20" t="inlineStr"/>
       <c r="K12" s="20" t="inlineStr"/>
@@ -2036,7 +2064,11 @@
       <c r="E13" s="21" t="inlineStr"/>
       <c r="F13" s="21" t="inlineStr"/>
       <c r="G13" s="21" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr"/>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I13" s="21" t="inlineStr"/>
       <c r="J13" s="21" t="inlineStr"/>
       <c r="K13" s="21" t="inlineStr"/>
@@ -2077,7 +2109,11 @@
       <c r="E14" s="21" t="inlineStr"/>
       <c r="F14" s="21" t="inlineStr"/>
       <c r="G14" s="21" t="inlineStr"/>
-      <c r="H14" s="21" t="inlineStr"/>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I14" s="21" t="inlineStr"/>
       <c r="J14" s="21" t="inlineStr"/>
       <c r="K14" s="21" t="inlineStr"/>
@@ -2118,7 +2154,11 @@
       <c r="E15" s="21" t="inlineStr"/>
       <c r="F15" s="21" t="inlineStr"/>
       <c r="G15" s="21" t="inlineStr"/>
-      <c r="H15" s="21" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I15" s="21" t="inlineStr"/>
       <c r="J15" s="21" t="inlineStr"/>
       <c r="K15" s="21" t="inlineStr"/>
@@ -2159,7 +2199,11 @@
       <c r="E16" s="21" t="inlineStr"/>
       <c r="F16" s="21" t="inlineStr"/>
       <c r="G16" s="21" t="inlineStr"/>
-      <c r="H16" s="21" t="inlineStr"/>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I16" s="21" t="inlineStr"/>
       <c r="J16" s="21" t="inlineStr"/>
       <c r="K16" s="21" t="inlineStr"/>
@@ -2194,7 +2238,11 @@
       <c r="E17" s="28" t="inlineStr"/>
       <c r="F17" s="28" t="inlineStr"/>
       <c r="G17" s="28" t="inlineStr"/>
-      <c r="H17" s="28" t="inlineStr"/>
+      <c r="H17" s="32" t="inlineStr">
+        <is>
+          <t>ชาญวิทย์</t>
+        </is>
+      </c>
       <c r="I17" s="28" t="inlineStr"/>
       <c r="J17" s="28" t="inlineStr"/>
       <c r="K17" s="28" t="inlineStr"/>

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -1754,7 +1754,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="20" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="20" t="inlineStr"/>
@@ -1799,7 +1803,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr"/>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="20" t="inlineStr"/>
       <c r="K7" s="20" t="inlineStr"/>
       <c r="L7" s="20" t="inlineStr"/>
@@ -1844,7 +1852,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr"/>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="20" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="inlineStr"/>
@@ -1889,7 +1901,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="20" t="inlineStr"/>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
@@ -1934,7 +1950,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="20" t="inlineStr"/>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="20" t="inlineStr"/>
       <c r="K10" s="20" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr"/>
@@ -1979,7 +1999,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="20" t="inlineStr"/>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="20" t="inlineStr"/>
       <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
@@ -2024,7 +2048,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J12" s="20" t="inlineStr"/>
       <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
@@ -2069,7 +2097,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr"/>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J13" s="21" t="inlineStr"/>
       <c r="K13" s="21" t="inlineStr"/>
       <c r="L13" s="21" t="inlineStr"/>
@@ -2114,7 +2146,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr"/>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J14" s="21" t="inlineStr"/>
       <c r="K14" s="21" t="inlineStr"/>
       <c r="L14" s="21" t="inlineStr"/>
@@ -2159,7 +2195,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr"/>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J15" s="21" t="inlineStr"/>
       <c r="K15" s="21" t="inlineStr"/>
       <c r="L15" s="21" t="inlineStr"/>
@@ -2204,7 +2244,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I16" s="21" t="inlineStr"/>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J16" s="21" t="inlineStr"/>
       <c r="K16" s="21" t="inlineStr"/>
       <c r="L16" s="21" t="inlineStr"/>
@@ -2243,7 +2287,11 @@
           <t>ชาญวิทย์</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr"/>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>ขวัญชัย</t>
+        </is>
+      </c>
       <c r="J17" s="28" t="inlineStr"/>
       <c r="K17" s="28" t="inlineStr"/>
       <c r="L17" s="28" t="inlineStr"/>

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -2359,7 +2359,7 @@
       <c r="F19" s="25" t="inlineStr"/>
       <c r="G19" s="25" t="inlineStr"/>
       <c r="H19" s="25" t="inlineStr"/>
-      <c r="I19" s="25" t="inlineStr"/>
+      <c r="I19" s="35" t="inlineStr"/>
       <c r="J19" s="25" t="inlineStr"/>
       <c r="K19" s="25" t="inlineStr"/>
       <c r="L19" s="25" t="inlineStr"/>

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -1759,7 +1759,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="20" t="inlineStr"/>
       <c r="L6" s="20" t="inlineStr"/>
       <c r="M6" s="20" t="inlineStr"/>
@@ -1808,7 +1812,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr"/>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="20" t="inlineStr"/>
       <c r="L7" s="20" t="inlineStr"/>
       <c r="M7" s="20" t="inlineStr"/>
@@ -1857,7 +1865,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr"/>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="20" t="inlineStr"/>
       <c r="L8" s="20" t="inlineStr"/>
       <c r="M8" s="20" t="inlineStr"/>
@@ -1906,7 +1918,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="20" t="inlineStr"/>
       <c r="L9" s="20" t="inlineStr"/>
       <c r="M9" s="20" t="inlineStr"/>
@@ -1955,7 +1971,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr"/>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="20" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr"/>
       <c r="M10" s="20" t="inlineStr"/>
@@ -2004,7 +2024,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr"/>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="20" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr"/>
       <c r="M11" s="20" t="inlineStr"/>
@@ -2053,7 +2077,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="K12" s="20" t="inlineStr"/>
       <c r="L12" s="20" t="inlineStr"/>
       <c r="M12" s="20" t="inlineStr"/>
@@ -2102,7 +2130,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J13" s="21" t="inlineStr"/>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K13" s="21" t="inlineStr"/>
       <c r="L13" s="21" t="inlineStr"/>
       <c r="M13" s="21" t="inlineStr"/>
@@ -2151,7 +2183,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J14" s="21" t="inlineStr"/>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K14" s="21" t="inlineStr"/>
       <c r="L14" s="21" t="inlineStr"/>
       <c r="M14" s="21" t="inlineStr"/>
@@ -2200,7 +2236,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K15" s="21" t="inlineStr"/>
       <c r="L15" s="21" t="inlineStr"/>
       <c r="M15" s="21" t="inlineStr"/>
@@ -2249,7 +2289,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J16" s="21" t="inlineStr"/>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K16" s="21" t="inlineStr"/>
       <c r="L16" s="21" t="inlineStr"/>
       <c r="M16" s="21" t="inlineStr"/>

--- a/FM-MN-07_MILLING-04.xlsx
+++ b/FM-MN-07_MILLING-04.xlsx
@@ -1765,7 +1765,11 @@
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="20" t="inlineStr"/>
       <c r="N6" s="20" t="inlineStr"/>
       <c r="O6" s="20" t="inlineStr"/>
@@ -1818,7 +1822,11 @@
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="20" t="inlineStr"/>
       <c r="N7" s="20" t="inlineStr"/>
       <c r="O7" s="20" t="inlineStr"/>
@@ -1871,7 +1879,11 @@
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="20" t="inlineStr"/>
       <c r="N8" s="20" t="inlineStr"/>
       <c r="O8" s="20" t="inlineStr"/>
@@ -1924,7 +1936,11 @@
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="20" t="inlineStr"/>
       <c r="N9" s="20" t="inlineStr"/>
       <c r="O9" s="20" t="inlineStr"/>
@@ -1977,7 +1993,11 @@
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="20" t="inlineStr"/>
       <c r="N10" s="20" t="inlineStr"/>
       <c r="O10" s="20" t="inlineStr"/>
@@ -2030,7 +2050,11 @@
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="20" t="inlineStr"/>
       <c r="N11" s="20" t="inlineStr"/>
       <c r="O11" s="20" t="inlineStr"/>
@@ -2083,7 +2107,11 @@
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="M12" s="20" t="inlineStr"/>
       <c r="N12" s="20" t="inlineStr"/>
       <c r="O12" s="20" t="inlineStr"/>
@@ -2136,7 +2164,11 @@
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr"/>
-      <c r="L13" s="21" t="inlineStr"/>
+      <c r="L13" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M13" s="21" t="inlineStr"/>
       <c r="N13" s="21" t="inlineStr"/>
       <c r="O13" s="21" t="inlineStr"/>
@@ -2189,7 +2221,11 @@
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr"/>
-      <c r="L14" s="21" t="inlineStr"/>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M14" s="21" t="inlineStr"/>
       <c r="N14" s="21" t="inlineStr"/>
       <c r="O14" s="21" t="inlineStr"/>
@@ -2242,7 +2278,11 @@
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr"/>
-      <c r="L15" s="21" t="inlineStr"/>
+      <c r="L15" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M15" s="21" t="inlineStr"/>
       <c r="N15" s="21" t="inlineStr"/>
       <c r="O15" s="21" t="inlineStr"/>
@@ -2295,7 +2335,11 @@
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr"/>
-      <c r="L16" s="21" t="inlineStr"/>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M16" s="21" t="inlineStr"/>
       <c r="N16" s="21" t="inlineStr"/>
       <c r="O16" s="21" t="inlineStr"/>
